--- a/data/pack/eu/diesel.xlsx
+++ b/data/pack/eu/diesel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1088"/>
+  <dimension ref="A1:K1089"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -60081,7 +60081,7 @@
         </is>
       </c>
       <c r="E1085" t="n">
-        <v>2.158736194167926</v>
+        <v>2.158839599924761</v>
       </c>
       <c r="F1085" t="inlineStr">
         <is>
@@ -60274,6 +60274,61 @@
         </is>
       </c>
       <c r="K1088" t="inlineStr">
+        <is>
+          <t>Source: European Commission (Weekly Oil Bulletin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Gasóleo de automoción (surtidor)</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="E1089" t="n">
+        <v>2.135879318361865</v>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>European Commission — Weekly Oil Bulletin (DG ENER)</t>
+        </is>
+      </c>
+      <c r="J1089" t="inlineStr">
+        <is>
+          <t>EU-REUSE-2011-833</t>
+        </is>
+      </c>
+      <c r="K1089" t="inlineStr">
         <is>
           <t>Source: European Commission (Weekly Oil Bulletin)</t>
         </is>
@@ -60377,7 +60432,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
@@ -60388,7 +60443,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="9">
@@ -60483,7 +60538,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>

--- a/data/pack/eu/diesel.xlsx
+++ b/data/pack/eu/diesel.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1089"/>
+  <dimension ref="A1:K1090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -60301,7 +60301,7 @@
         </is>
       </c>
       <c r="E1089" t="n">
-        <v>2.135879318361865</v>
+        <v>2.135720907391608</v>
       </c>
       <c r="F1089" t="inlineStr">
         <is>
@@ -60329,6 +60329,61 @@
         </is>
       </c>
       <c r="K1089" t="inlineStr">
+        <is>
+          <t>Source: European Commission (Weekly Oil Bulletin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Gasóleo de automoción (surtidor)</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E1090" t="n">
+        <v>2.138675613493391</v>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>European Commission — Weekly Oil Bulletin (DG ENER)</t>
+        </is>
+      </c>
+      <c r="J1090" t="inlineStr">
+        <is>
+          <t>EU-REUSE-2011-833</t>
+        </is>
+      </c>
+      <c r="K1090" t="inlineStr">
         <is>
           <t>Source: European Commission (Weekly Oil Bulletin)</t>
         </is>
@@ -60432,7 +60487,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -60443,7 +60498,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="9">
@@ -60538,7 +60593,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>

--- a/data/pack/eu/diesel.xlsx
+++ b/data/pack/eu/diesel.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1090"/>
+  <dimension ref="A1:K1091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -60384,6 +60384,61 @@
         </is>
       </c>
       <c r="K1090" t="inlineStr">
+        <is>
+          <t>Source: European Commission (Weekly Oil Bulletin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>diesel</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>Gasóleo de automoción (surtidor)</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="E1091" t="n">
+        <v>2.146185973890054</v>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>litro</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>European Commission — Weekly Oil Bulletin (DG ENER)</t>
+        </is>
+      </c>
+      <c r="J1091" t="inlineStr">
+        <is>
+          <t>EU-REUSE-2011-833</t>
+        </is>
+      </c>
+      <c r="K1091" t="inlineStr">
         <is>
           <t>Source: European Commission (Weekly Oil Bulletin)</t>
         </is>
@@ -60487,7 +60542,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -60498,7 +60553,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="9">
@@ -60593,7 +60648,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
